--- a/output/pdf_financials_xlsx/RS.xlsx
+++ b/output/pdf_financials_xlsx/RS.xlsx
@@ -911,10 +911,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>2.461864</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>3.710358</v>
       </c>
     </row>
     <row r="35">
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>2.461864</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>3.710358</v>
       </c>
     </row>
     <row r="37">
@@ -2370,7 +2370,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">

--- a/output/pdf_financials_xlsx/RS.xlsx
+++ b/output/pdf_financials_xlsx/RS.xlsx
@@ -2006,10 +2006,10 @@
         </is>
       </c>
       <c r="B115" s="3" t="n">
-        <v>0</v>
+        <v>1.091898</v>
       </c>
       <c r="C115" s="3" t="n">
-        <v>0</v>
+        <v>21.524868</v>
       </c>
     </row>
     <row r="116">
@@ -2820,7 +2820,11 @@
           <t>Proceeds from Sale of Investments</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E20" s="5" t="n">
         <v>1.091898</v>
       </c>
@@ -4270,7 +4274,11 @@
           <t>Net Investment Profit (Loss) before Distributions on Preferred Shares</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr"/>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>PreferredStockDividends</t>
+        </is>
+      </c>
       <c r="E78" s="5" t="n">
         <v>-0.15413</v>
       </c>
@@ -4294,7 +4302,11 @@
           <t>Distributions on Preferred Shares (Note 11)</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr"/>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>PreferredStockDividends</t>
+        </is>
+      </c>
       <c r="E79" s="5" t="n">
         <v>0.099012</v>
       </c>
